--- a/salidas/tabla_allega_cso_pond.xlsx
+++ b/salidas/tabla_allega_cso_pond.xlsx
@@ -17,19 +17,19 @@
     <t xml:space="preserve"/>
   </si>
   <si>
-    <t xml:space="preserve">Clase directivo-profesional</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clase media rutinaria</t>
+    <t xml:space="preserve">Directiva-profesional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Media rutinaria</t>
   </si>
   <si>
     <t xml:space="preserve">Pequeña burguesía</t>
   </si>
   <si>
-    <t xml:space="preserve">Clase obrera calificada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clase obrera no calificada</t>
+    <t xml:space="preserve">Obrera calificada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Obrera no calificada</t>
   </si>
   <si>
     <t xml:space="preserve">Sin allegamiento</t>
@@ -389,19 +389,19 @@
         <v>6</v>
       </c>
       <c r="B2" t="n">
-        <v>870.891430442646</v>
+        <v>611478</v>
       </c>
       <c r="C2" t="n">
-        <v>1593.6075425706</v>
+        <v>877019</v>
       </c>
       <c r="D2" t="n">
-        <v>465.148610899246</v>
+        <v>271878</v>
       </c>
       <c r="E2" t="n">
-        <v>1013.51532494354</v>
+        <v>1011828</v>
       </c>
       <c r="F2" t="n">
-        <v>699.159307663796</v>
+        <v>399872</v>
       </c>
     </row>
     <row r="3">
@@ -409,19 +409,19 @@
         <v>7</v>
       </c>
       <c r="B3" t="n">
-        <v>33.9599148408576</v>
+        <v>36137</v>
       </c>
       <c r="C3" t="n">
-        <v>104.992275085885</v>
+        <v>139243</v>
       </c>
       <c r="D3" t="n">
-        <v>30.4705481219678</v>
+        <v>33922</v>
       </c>
       <c r="E3" t="n">
-        <v>50.1727272118908</v>
+        <v>110747</v>
       </c>
       <c r="F3" t="n">
-        <v>68.1411641015767</v>
+        <v>78807</v>
       </c>
     </row>
   </sheetData>
